--- a/서버정보/20260708_리소스배포_운영.xlsx
+++ b/서버정보/20260708_리소스배포_운영.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D973416-A745-4359-A814-2BB256ED5083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A224D2C8-1583-49E8-9A93-C5DA0B9C72E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7105" uniqueCount="1070">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7107" uniqueCount="1072">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5582,6 +5582,14 @@
   </si>
   <si>
     <t>hazr-p-dtg-bbigeoap-lb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DTG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-dtg-rg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -32943,12 +32951,11 @@
       <c r="B149" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C149" s="74" t="str" cm="1">
-        <f t="array" ref="C149">UPPER(INDEX(_xlfn.TEXTSPLIT($D149, "-"), 3))</f>
-        <v>BDP</v>
+      <c r="C149" s="74" t="s">
+        <v>1070</v>
       </c>
       <c r="D149" s="80" t="s">
-        <v>316</v>
+        <v>1071</v>
       </c>
       <c r="E149" s="86" t="s">
         <v>24</v>
@@ -32997,12 +33004,11 @@
       <c r="B150" s="73" t="s">
         <v>23</v>
       </c>
-      <c r="C150" s="73" t="str" cm="1">
-        <f t="array" ref="C150">UPPER(INDEX(_xlfn.TEXTSPLIT($D150, "-"), 3))</f>
-        <v>BDP</v>
+      <c r="C150" s="73" t="s">
+        <v>1070</v>
       </c>
       <c r="D150" s="78" t="s">
-        <v>316</v>
+        <v>1071</v>
       </c>
       <c r="E150" s="85" t="s">
         <v>24</v>
@@ -46034,6 +46040,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -46177,35 +46198,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -46227,9 +46223,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>